--- a/artfynd/A 22840-2023 artfynd.xlsx
+++ b/artfynd/A 22840-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 22840-2023 artfynd.xlsx
+++ b/artfynd/A 22840-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>80766454</v>
       </c>
       <c r="B2" t="n">
-        <v>96254</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99038</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>557255.6829550472</v>
+        <v>557256</v>
       </c>
       <c r="R2" t="n">
-        <v>6620161.03787436</v>
+        <v>6620161</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -748,19 +743,9 @@
           <t>2019-07-07</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-07-07</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,10 +766,122 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sören Larsson, Greta Larsson</t>
+          <t>Greta Larsson, Sören Larsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>125978017</v>
+      </c>
+      <c r="B3" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Uggelbovägen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>557291</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6620012</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>och blomknopp.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Grus/sandmark, fuktpåverkad</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Tom Sävström, Lennart Eriksson R, Mikael mälberg, Lise-Lotte Norin, Kerstin Aneusson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22840-2023 artfynd.xlsx
+++ b/artfynd/A 22840-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>80766454</v>
+        <v>134769369</v>
       </c>
       <c r="B2" t="n">
-        <v>99038</v>
+        <v>106199</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,45 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223597</v>
+        <v>221154</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Skogsstjärna</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Lysimachia europaea</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(L.) U. Manns &amp; Anderb.</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Värsmossen, Sura sn, Vstm</t>
+          <t>Ursjötorp, Sura sn, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>557256</v>
+        <v>557284</v>
       </c>
       <c r="R2" t="n">
-        <v>6620161</v>
+        <v>6620017</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,12 +748,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-07-07</t>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-07-07</t>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -766,17 +784,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Greta Larsson, Sören Larsson</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125978017</v>
+        <v>134769377</v>
       </c>
       <c r="B3" t="n">
-        <v>99038</v>
+        <v>98063</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -784,19 +802,23 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>223597</v>
+        <v>221946</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
@@ -808,17 +830,17 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Uggelbovägen, Vstm</t>
+          <t>Ursjötorp, Sura sn, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>557291</v>
+        <v>557284</v>
       </c>
       <c r="R3" t="n">
-        <v>6620012</v>
+        <v>6620017</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -842,17 +864,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>och blomknopp.</t>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -865,23 +892,929 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Grus/sandmark, fuktpåverkad</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>134769298</v>
+      </c>
+      <c r="B4" t="n">
+        <v>103764</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222004</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kärrviol</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Viola palustris</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ursjötorp, Sura sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>557284</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6620017</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>134769445</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99853</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222306</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Stjärnstarr</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Carex echinata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Murray</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ursjötorp, Sura sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>557284</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6620017</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>134769296</v>
+      </c>
+      <c r="B6" t="n">
+        <v>101324</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222782</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vitsippa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Anemone nemorosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ursjötorp, Sura sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>557284</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6620017</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>134769496</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98249</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ursjötorp, Sura sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>557313</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6620035</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>80766454</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Värsmossen, Sura sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>557256</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6620161</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2019-07-07</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2019-07-07</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Greta Larsson, Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>125978017</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Uggelbovägen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>557291</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6620012</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>och blomknopp.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Grus/sandmark, fuktpåverkad</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
           <t>Tom Sävström</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX9" t="inlineStr">
         <is>
           <t>Tom Sävström, Lennart Eriksson R, Mikael mälberg, Lise-Lotte Norin, Kerstin Aneusson</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>134769322</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99115</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ursjötorp, Sura sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>557284</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6620017</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ca-antal</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>134769501</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99115</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Ursjötorp, Sura sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>557313</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6620035</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22840-2023 artfynd.xlsx
+++ b/artfynd/A 22840-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134769369</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134769377</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1020,6 +1035,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134769298</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1136,6 +1156,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134769445</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1252,6 +1277,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134769296</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1368,6 +1398,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134769496</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1466,6 +1501,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80766454</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1578,6 +1618,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125978017</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1699,6 +1744,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134769322</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1815,8 +1865,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134769501</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>